--- a/outputs/2026-02-04/valid_entity_sharing.xlsx
+++ b/outputs/2026-02-04/valid_entity_sharing.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3254</v>
+        <v>9683</v>
       </c>
     </row>
     <row r="3">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>999</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>441</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="5">
@@ -502,133 +502,133 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>440</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Menigo</t>
+          <t>Brakes</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Servicestyckarna</t>
+          <t>KFF</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>337</v>
+        <v>861</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brakes</t>
+          <t>Menigo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KFF</t>
+          <t>Servicestyckarna</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>252</v>
+        <v>337</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Menigo</t>
+          <t>Brakes</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sysco_Northern_Ireland</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>155</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fruktservice</t>
+          <t>Brakes</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Menigo</t>
+          <t>Fresh_Direct</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>131</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brakes</t>
+          <t>KFF</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fresh_Direct</t>
+          <t>Sysco_Northern_Ireland</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>86</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Classic_Drinks</t>
+          <t>KFF</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Menigo</t>
+          <t>Sysco_ROI</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brakes</t>
+          <t>Menigo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Sysco_Northern_Ireland</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Menigo</t>
+          <t>KFF</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sysco_ROI</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brakes</t>
+          <t>Fruktservice</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -637,28 +637,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KFF</t>
+          <t>Brakes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sysco_ROI</t>
+          <t>Menigo</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KFF</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -667,67 +667,67 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KFF</t>
+          <t>Brakes</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Sysco_France</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>47</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sysco_France</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sysco_Northern_Ireland</t>
+          <t>Sysco_ROI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>39</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Brakes</t>
+          <t>Sysco_France</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sysco_France</t>
+          <t>Sysco_Northern_Ireland</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ekofisk</t>
+          <t>Menigo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Menigo</t>
+          <t>Sysco_ROI</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>36</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21">
@@ -742,52 +742,52 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>35</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Classic_Drinks</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>Menigo</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Sysco_France</t>
-        </is>
-      </c>
       <c r="C22" t="n">
-        <v>32</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Menigo</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sysco_ROI</t>
+          <t>Sysco_France</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Fresh_Direct</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sysco_Northern_Ireland</t>
+          <t>Sysco_ROI</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
@@ -798,11 +798,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sysco_ROI</t>
+          <t>Sysco_Northern_Ireland</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26">
@@ -813,56 +813,56 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sysco_Northern_Ireland</t>
+          <t>KFF</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Classic_Drinks</t>
+          <t>Ekofisk</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sysco_ROI</t>
+          <t>Menigo</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Fresh_Direct</t>
+          <t>Classic_Drinks</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>KFF</t>
+          <t>Sysco_ROI</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KFF</t>
+          <t>Brakes</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sysco_France</t>
+          <t>Classic_Drinks</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30">
@@ -877,37 +877,37 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Brakes</t>
+          <t>KFF</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Classic_Drinks</t>
+          <t>Sysco_France</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ready_Chef</t>
+          <t>Fresh_Direct</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sysco_ROI</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
@@ -922,58 +922,58 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Medina</t>
+          <t>Ready_Chef</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sysco_France</t>
+          <t>Sysco_ROI</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Fresh_Direct</t>
+          <t>Medina</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Menigo</t>
+          <t>Sysco_France</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ready_Chef</t>
+          <t>Fresh_Direct</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sysco_Northern_Ireland</t>
+          <t>Menigo</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Fresh_Direct</t>
+          <t>Classic_Drinks</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -982,36 +982,66 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Classic_Drinks</t>
+          <t>Ready_Chef</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fresh_Direct</t>
+          <t>Sysco_Northern_Ireland</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Classic_Drinks</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Fresh_Direct</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Classic_Drinks</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>KFF</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>LAG</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Sysco_France</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C41" t="n">
         <v>1</v>
       </c>
     </row>
